--- a/441-rc---tdduipatient-birthdate/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/441-rc---tdduipatient-birthdate/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3450" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4038" uniqueCount="642">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T15:34:05+00:00</t>
+    <t>2026-02-26T16:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -868,6 +868,51 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
+    <t>Encounter.identifier:AdministrativeFileNumber</t>
+  </si>
+  <si>
+    <t>AdministrativeFileNumber</t>
+  </si>
+  <si>
+    <t>Numéro de dossier administratif du séjour</t>
+  </si>
+  <si>
+    <t>numeroDossierAdministratifSejour</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.id</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.extension</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.use</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-encounter-identifier"/&gt;
+    &lt;code value="NUMDOSS"/&gt;
+    &lt;display value="Numéro de dossier administratif du séjour"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.system</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.value</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.period</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.assigner</t>
+  </si>
+  <si>
     <t>Encounter.status</t>
   </si>
   <si>
@@ -1055,10 +1100,10 @@
     <t>Broad categorization of the service that is to be provided (e.g. cardiology).</t>
   </si>
   <si>
-    <t>Broad categorization of the service that is to be provided.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J226-ModaliteAccueil-ROR/FHIR/JDV-J226-ModaliteAccueil-ROR</t>
+  </si>
+  <si>
+    <t>modaliteAccueil</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -1254,6 +1299,92 @@
   </si>
   <si>
     <t>ROL-4</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
+    <t>origineDemande</t>
   </si>
   <si>
     <t>Encounter.appointment</t>
@@ -1550,6 +1681,25 @@
     <t>Encounter.hospitalization.extension</t>
   </si>
   <si>
+    <t>Encounter.hospitalization.extension:TDDUIEntryDateOrigin</t>
+  </si>
+  <si>
+    <t>TDDUIEntryDateOrigin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-entry-date-origin}
+</t>
+  </si>
+  <si>
+    <t>TDDUI Entry Date Origin</t>
+  </si>
+  <si>
+    <t>Extension permettant de véhiculer la date d'entrée dans l'ESSMS de provenance.</t>
+  </si>
+  <si>
+    <t>dateEntreeESSMSProvenance</t>
+  </si>
+  <si>
     <t>Encounter.hospitalization.modifierExtension</t>
   </si>
   <si>
@@ -1562,136 +1712,146 @@
     <t>Pre-admission identifier.</t>
   </si>
   <si>
+    <t>numeroDossierESSMSProvenance</t>
+  </si>
+  <si>
     <t>PV1-5</t>
   </si>
   <si>
     <t>Encounter.hospitalization.origin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
+</t>
+  </si>
+  <si>
+    <t>The location/organization from which the patient came before admission</t>
+  </si>
+  <si>
+    <t>The location/organization from which the patient came before admission.</t>
+  </si>
+  <si>
+    <t>ESSMSProvenance</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=ORG].role</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.admitSource</t>
+  </si>
+  <si>
+    <t>From where patient was admitted (physician referral, transfer)</t>
+  </si>
+  <si>
+    <t>From where patient was admitted (physician referral, transfer).</t>
+  </si>
+  <si>
+    <t>From where the patient was admitted.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
+  </si>
+  <si>
+    <t>.admissionReferralSourceCode</t>
+  </si>
+  <si>
+    <t>PV1-14</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.reAdmission</t>
+  </si>
+  <si>
+    <t>The type of hospital re-admission that has occurred (if any). If the value is absent, then this is not identified as a readmission</t>
+  </si>
+  <si>
+    <t>Whether this hospitalization is a readmission and why if known.</t>
+  </si>
+  <si>
+    <t>The reason for re-admission of this hospitalization encounter.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+  </si>
+  <si>
+    <t>PV1-13</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dietPreference</t>
+  </si>
+  <si>
+    <t>Diet preferences reported by the patient</t>
+  </si>
+  <si>
+    <t>Diet preferences reported by the patient.</t>
+  </si>
+  <si>
+    <t>For example, a patient may request both a dairy-free and nut-free diet preference (not mutually exclusive).</t>
+  </si>
+  <si>
+    <t>Used to track patient's diet restrictions and/or preference. For a complete description of the nutrition needs of a patient during their stay, one should use the nutritionOrder resource which links to Encounter.</t>
+  </si>
+  <si>
+    <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
+  </si>
+  <si>
+    <t>PV1-38</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialCourtesy</t>
+  </si>
+  <si>
+    <t>Special courtesies (VIP, board member)</t>
+  </si>
+  <si>
+    <t>Special courtesies (VIP, board member).</t>
+  </si>
+  <si>
+    <t>Special courtesies.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
+  </si>
+  <si>
+    <t>.specialCourtesiesCode</t>
+  </si>
+  <si>
+    <t>PV1-16</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialArrangement</t>
+  </si>
+  <si>
+    <t>Wheelchair, translator, stretcher, etc.</t>
+  </si>
+  <si>
+    <t>Any special requests that have been made for this hospitalization encounter, such as the provision of specific equipment or other things.</t>
+  </si>
+  <si>
+    <t>Special arrangements.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
+  </si>
+  <si>
+    <t>.specialArrangementCode</t>
+  </si>
+  <si>
+    <t>PV1-15 / OBR-30 / OBR-43</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.destination</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Location|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
-    <t>The location/organization from which the patient came before admission</t>
-  </si>
-  <si>
-    <t>The location/organization from which the patient came before admission.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=ORG].role</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.admitSource</t>
-  </si>
-  <si>
-    <t>From where patient was admitted (physician referral, transfer)</t>
-  </si>
-  <si>
-    <t>From where patient was admitted (physician referral, transfer).</t>
-  </si>
-  <si>
-    <t>From where the patient was admitted.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
-  </si>
-  <si>
-    <t>.admissionReferralSourceCode</t>
-  </si>
-  <si>
-    <t>PV1-14</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.reAdmission</t>
-  </si>
-  <si>
-    <t>The type of hospital re-admission that has occurred (if any). If the value is absent, then this is not identified as a readmission</t>
-  </si>
-  <si>
-    <t>Whether this hospitalization is a readmission and why if known.</t>
-  </si>
-  <si>
-    <t>The reason for re-admission of this hospitalization encounter.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
-  </si>
-  <si>
-    <t>PV1-13</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dietPreference</t>
-  </si>
-  <si>
-    <t>Diet preferences reported by the patient</t>
-  </si>
-  <si>
-    <t>Diet preferences reported by the patient.</t>
-  </si>
-  <si>
-    <t>For example, a patient may request both a dairy-free and nut-free diet preference (not mutually exclusive).</t>
-  </si>
-  <si>
-    <t>Used to track patient's diet restrictions and/or preference. For a complete description of the nutrition needs of a patient during their stay, one should use the nutritionOrder resource which links to Encounter.</t>
-  </si>
-  <si>
-    <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
-  </si>
-  <si>
-    <t>PV1-38</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.specialCourtesy</t>
-  </si>
-  <si>
-    <t>Special courtesies (VIP, board member)</t>
-  </si>
-  <si>
-    <t>Special courtesies (VIP, board member).</t>
-  </si>
-  <si>
-    <t>Special courtesies.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
-  </si>
-  <si>
-    <t>.specialCourtesiesCode</t>
-  </si>
-  <si>
-    <t>PV1-16</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.specialArrangement</t>
-  </si>
-  <si>
-    <t>Wheelchair, translator, stretcher, etc.</t>
-  </si>
-  <si>
-    <t>Any special requests that have been made for this hospitalization encounter, such as the provision of specific equipment or other things.</t>
-  </si>
-  <si>
-    <t>Special arrangements.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
-  </si>
-  <si>
-    <t>.specialArrangementCode</t>
-  </si>
-  <si>
-    <t>PV1-15 / OBR-30 / OBR-43</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.destination</t>
-  </si>
-  <si>
     <t>Location/organization to which the patient is discharged</t>
   </si>
   <si>
@@ -1823,17 +1983,13 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
-</t>
-  </si>
-  <si>
     <t>The organization (facility) responsible for this encounter</t>
   </si>
   <si>
     <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
   </si>
   <si>
-    <t>EntiteJuridique</t>
+    <t>ESSMSAccueil</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>
@@ -2165,10 +2321,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO93"/>
+  <dimension ref="A1:AO109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.37890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.16015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2193,7 +2349,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="64.00390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.0859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.5625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -5255,15 +5411,17 @@
         <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>
@@ -5272,23 +5430,21 @@
         <v>81</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5313,13 +5469,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5337,13 +5493,13 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>271</v>
+        <v>186</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
@@ -5352,27 +5508,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>277</v>
+        <v>191</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>192</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>193</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5383,7 +5539,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5395,17 +5551,15 @@
         <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>202</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5454,19 +5608,19 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>204</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
@@ -5486,21 +5640,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>286</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -5512,15 +5666,17 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5557,31 +5713,31 @@
         <v>81</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
@@ -5601,44 +5757,46 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5662,13 +5820,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5686,19 +5844,19 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
@@ -5707,56 +5865,56 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>288</v>
+        <v>224</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>226</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>291</v>
+        <v>227</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5766,7 +5924,7 @@
         <v>81</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>81</v>
+        <v>279</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>81</v>
@@ -5781,13 +5939,11 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -5805,19 +5961,19 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
@@ -5826,21 +5982,21 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>81</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>235</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5860,19 +6016,23 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5881,10 +6041,10 @@
         <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>81</v>
@@ -5896,13 +6056,13 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -5920,10 +6080,10 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>293</v>
+        <v>242</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>90</v>
@@ -5941,21 +6101,21 @@
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5975,18 +6135,20 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5999,7 +6161,7 @@
         <v>81</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>81</v>
@@ -6035,10 +6197,10 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>251</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -6056,21 +6218,21 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>81</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>255</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6078,7 +6240,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -6093,13 +6255,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>256</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>257</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6126,13 +6288,13 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -6150,10 +6312,10 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>90</v>
@@ -6171,21 +6333,21 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>306</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6196,7 +6358,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6205,18 +6367,20 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6265,13 +6429,13 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
@@ -6286,21 +6450,21 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>205</v>
+        <v>269</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>81</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6308,7 +6472,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>90</v>
@@ -6317,21 +6481,23 @@
         <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>201</v>
+        <v>110</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>202</v>
+        <v>285</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6356,13 +6522,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -6380,10 +6546,10 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>204</v>
+        <v>284</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>90</v>
@@ -6392,34 +6558,34 @@
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>205</v>
+        <v>291</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6438,16 +6604,16 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>295</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>208</v>
+        <v>296</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>209</v>
+        <v>297</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>183</v>
+        <v>298</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6497,7 +6663,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>211</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6509,7 +6675,7 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6529,46 +6695,42 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>290</v>
+        <v>202</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6616,19 +6778,19 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>292</v>
+        <v>204</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6637,7 +6799,7 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6648,21 +6810,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6674,15 +6836,17 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>298</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>314</v>
+        <v>208</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6707,13 +6871,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6731,19 +6895,19 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>313</v>
+        <v>211</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6763,42 +6927,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6846,19 +7014,19 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -6867,7 +7035,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6878,10 +7046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6889,10 +7057,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6901,20 +7069,18 @@
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6939,13 +7105,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>324</v>
+        <v>288</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6963,13 +7129,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6981,24 +7147,24 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>327</v>
+        <v>205</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>328</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7006,7 +7172,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
@@ -7018,16 +7184,16 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7054,13 +7220,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7078,10 +7244,10 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -7096,7 +7262,7 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>205</v>
@@ -7105,15 +7271,15 @@
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7121,7 +7287,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -7133,16 +7299,16 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7169,13 +7335,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -7193,10 +7359,10 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>90</v>
@@ -7214,32 +7380,32 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>341</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>343</v>
+        <v>81</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
@@ -7248,20 +7414,18 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7310,13 +7474,13 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
@@ -7325,27 +7489,27 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>349</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>350</v>
+        <v>205</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>352</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7356,7 +7520,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7365,16 +7529,16 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>354</v>
+        <v>201</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>355</v>
+        <v>202</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>356</v>
+        <v>203</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7425,46 +7589,46 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>204</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>205</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>358</v>
+        <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>359</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>361</v>
+        <v>180</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7483,15 +7647,17 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>362</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>208</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7540,7 +7706,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>360</v>
+        <v>211</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7552,16 +7718,16 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>365</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>366</v>
+        <v>205</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7572,14 +7738,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>367</v>
+        <v>325</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>325</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7592,22 +7758,26 @@
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>282</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>368</v>
+        <v>303</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7655,7 +7825,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>305</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7667,30 +7837,30 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>371</v>
+        <v>133</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7698,7 +7868,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -7713,13 +7883,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>201</v>
+        <v>311</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>202</v>
+        <v>327</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>203</v>
+        <v>328</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7746,13 +7916,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7770,10 +7940,10 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>204</v>
+        <v>326</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>90</v>
@@ -7782,7 +7952,7 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7802,21 +7972,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7828,17 +7998,15 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>256</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>208</v>
+        <v>330</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -7887,19 +8055,19 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>211</v>
+        <v>329</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7919,14 +8087,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7939,26 +8107,24 @@
         <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>290</v>
+        <v>333</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>291</v>
+        <v>334</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7982,13 +8148,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -8006,7 +8172,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8018,30 +8184,30 @@
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>133</v>
+        <v>340</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8052,7 +8218,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -8067,14 +8233,12 @@
         <v>225</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8099,13 +8263,11 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8123,13 +8285,13 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
@@ -8138,27 +8300,27 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>381</v>
+        <v>339</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>382</v>
+        <v>205</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>383</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8181,13 +8343,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>385</v>
+        <v>349</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8214,13 +8376,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>81</v>
+        <v>351</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8238,7 +8400,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8259,29 +8421,29 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>387</v>
+        <v>352</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>388</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>90</v>
@@ -8296,15 +8458,17 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8353,7 +8517,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8368,27 +8532,27 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>81</v>
+        <v>361</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>396</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8411,13 +8575,13 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8468,7 +8632,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8486,35 +8650,35 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>401</v>
+        <v>205</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>81</v>
+        <v>371</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>402</v>
+        <v>372</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8526,17 +8690,15 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>256</v>
+        <v>375</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8585,13 +8747,13 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
@@ -8603,24 +8765,24 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>407</v>
+        <v>378</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>410</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8631,7 +8793,7 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8640,16 +8802,16 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>201</v>
+        <v>295</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>202</v>
+        <v>381</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>203</v>
+        <v>382</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8700,53 +8862,53 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>204</v>
+        <v>380</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>205</v>
+        <v>384</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>81</v>
+        <v>385</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8758,17 +8920,15 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8805,31 +8965,31 @@
         <v>81</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -8849,21 +9009,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -8872,19 +9032,19 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>414</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>415</v>
+        <v>208</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>416</v>
+        <v>209</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>417</v>
+        <v>183</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8934,82 +9094,82 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>211</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>421</v>
+        <v>205</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>414</v>
+        <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>424</v>
+        <v>303</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>425</v>
+        <v>304</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q59" t="s" s="2">
-        <v>427</v>
-      </c>
+      <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9053,42 +9213,42 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>428</v>
+        <v>305</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>429</v>
+        <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>430</v>
+        <v>133</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9099,7 +9259,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
@@ -9108,19 +9268,19 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>433</v>
+        <v>225</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>434</v>
+        <v>390</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>435</v>
+        <v>391</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>436</v>
+        <v>392</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9146,13 +9306,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9170,13 +9330,13 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
@@ -9188,35 +9348,35 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>437</v>
+        <v>395</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>438</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>439</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>439</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -9225,20 +9385,18 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>441</v>
+        <v>398</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9263,13 +9421,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9287,13 +9445,13 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>439</v>
+        <v>397</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
@@ -9305,35 +9463,35 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>449</v>
+        <v>401</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9345,17 +9503,15 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>451</v>
+        <v>403</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>452</v>
+        <v>404</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9404,13 +9560,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9422,24 +9578,24 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>446</v>
+        <v>406</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>447</v>
+        <v>407</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>448</v>
+        <v>408</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>449</v>
+        <v>409</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9450,7 +9606,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9459,16 +9615,16 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>454</v>
+        <v>202</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>455</v>
+        <v>203</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9519,19 +9675,19 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>453</v>
+        <v>204</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
@@ -9540,7 +9696,7 @@
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>456</v>
+        <v>205</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9551,21 +9707,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>457</v>
+        <v>411</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9577,15 +9733,17 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9622,31 +9780,31 @@
         <v>81</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -9666,21 +9824,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>412</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>412</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -9689,19 +9847,19 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>208</v>
+        <v>413</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>209</v>
+        <v>414</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>183</v>
+        <v>415</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9751,19 +9909,19 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>211</v>
+        <v>416</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>81</v>
@@ -9772,7 +9930,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9783,46 +9941,44 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>290</v>
+        <v>419</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>291</v>
+        <v>420</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -9846,13 +10002,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9870,19 +10026,19 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>292</v>
+        <v>424</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -9902,18 +10058,18 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>425</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>425</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>90</v>
@@ -9928,16 +10084,16 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>462</v>
+        <v>187</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>464</v>
+        <v>427</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9987,10 +10143,10 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>90</v>
@@ -10005,24 +10161,24 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>465</v>
+        <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>467</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>468</v>
+        <v>431</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>431</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10042,18 +10198,20 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>469</v>
+        <v>432</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10078,13 +10236,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>471</v>
+        <v>81</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>472</v>
+        <v>81</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10102,7 +10260,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>468</v>
+        <v>435</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10117,13 +10275,13 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10134,10 +10292,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10148,7 +10306,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10157,16 +10315,16 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10217,13 +10375,13 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
@@ -10235,24 +10393,24 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10263,7 +10421,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
@@ -10275,16 +10433,16 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>479</v>
+        <v>256</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>480</v>
+        <v>444</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>481</v>
+        <v>445</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>482</v>
+        <v>446</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10334,13 +10492,13 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
@@ -10352,24 +10510,24 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>483</v>
+        <v>448</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10392,17 +10550,15 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>485</v>
+        <v>202</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10451,7 +10607,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>484</v>
+        <v>204</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10463,7 +10619,7 @@
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -10472,7 +10628,7 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>488</v>
+        <v>205</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10483,21 +10639,21 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -10509,15 +10665,17 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10554,31 +10712,31 @@
         <v>81</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>81</v>
@@ -10598,21 +10756,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>490</v>
+        <v>453</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>490</v>
+        <v>453</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>81</v>
@@ -10621,19 +10779,19 @@
         <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>135</v>
+        <v>454</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>208</v>
+        <v>455</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>209</v>
+        <v>456</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>183</v>
+        <v>457</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10683,82 +10841,82 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>211</v>
+        <v>458</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>81</v>
+        <v>459</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>81</v>
+        <v>460</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>205</v>
+        <v>461</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>81</v>
+        <v>462</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>454</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>290</v>
+        <v>464</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>291</v>
+        <v>465</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q74" s="2"/>
+      <c r="Q74" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="R74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10802,42 +10960,42 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>292</v>
+        <v>468</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>81</v>
+        <v>459</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>81</v>
+        <v>469</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>133</v>
+        <v>470</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>81</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10860,15 +11018,17 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>187</v>
+        <v>473</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -10917,7 +11077,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10935,35 +11095,35 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>192</v>
+        <v>477</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>495</v>
+        <v>478</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
@@ -10972,18 +11132,20 @@
         <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>497</v>
+        <v>225</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -11008,13 +11170,13 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>81</v>
+        <v>484</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>81</v>
+        <v>485</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -11032,13 +11194,13 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
@@ -11050,35 +11212,35 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>81</v>
+        <v>486</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>81</v>
@@ -11087,18 +11249,20 @@
         <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>225</v>
+        <v>491</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11123,13 +11287,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>504</v>
+        <v>81</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -11147,13 +11311,13 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>81</v>
@@ -11165,24 +11329,24 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>81</v>
+        <v>486</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>507</v>
+        <v>489</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11193,7 +11357,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
@@ -11202,16 +11366,16 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>225</v>
+        <v>295</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11238,13 +11402,13 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>511</v>
+        <v>81</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -11262,13 +11426,13 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
@@ -11283,21 +11447,21 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>205</v>
+        <v>496</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>513</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11308,7 +11472,7 @@
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>81</v>
@@ -11320,20 +11484,16 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>515</v>
+        <v>202</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>81</v>
       </c>
@@ -11357,13 +11517,13 @@
         <v>81</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>520</v>
+        <v>81</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>81</v>
@@ -11381,19 +11541,19 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>514</v>
+        <v>204</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>81</v>
@@ -11402,25 +11562,25 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>521</v>
+        <v>205</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>522</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11439,15 +11599,17 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>524</v>
+        <v>208</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11472,13 +11634,13 @@
         <v>81</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>526</v>
+        <v>81</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>527</v>
+        <v>81</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>81</v>
@@ -11496,7 +11658,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>523</v>
+        <v>211</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11508,7 +11670,7 @@
         <v>81</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>81</v>
@@ -11517,25 +11679,25 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>528</v>
+        <v>205</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>529</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11548,22 +11710,26 @@
         <v>81</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>531</v>
+        <v>303</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>81</v>
       </c>
@@ -11587,13 +11753,13 @@
         <v>81</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>533</v>
+        <v>81</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>534</v>
+        <v>81</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>81</v>
@@ -11611,7 +11777,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>530</v>
+        <v>305</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11623,7 +11789,7 @@
         <v>81</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>81</v>
@@ -11632,29 +11798,29 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>535</v>
+        <v>133</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>536</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>90</v>
@@ -11666,18 +11832,20 @@
         <v>81</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>538</v>
+        <v>503</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -11726,10 +11894,10 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>90</v>
@@ -11744,24 +11912,24 @@
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>540</v>
+        <v>506</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>541</v>
+        <v>507</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11787,10 +11955,10 @@
         <v>225</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>544</v>
+        <v>510</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11817,13 +11985,13 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>323</v>
+        <v>114</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>545</v>
+        <v>511</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>546</v>
+        <v>512</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -11841,7 +12009,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11862,21 +12030,21 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>547</v>
+        <v>205</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>548</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11887,7 +12055,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
@@ -11899,17 +12067,15 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>282</v>
+        <v>514</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>550</v>
+        <v>515</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11958,13 +12124,13 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>81</v>
@@ -11979,7 +12145,7 @@
         <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>553</v>
+        <v>517</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
@@ -11990,10 +12156,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>554</v>
+        <v>518</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>554</v>
+        <v>518</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12004,7 +12170,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -12016,15 +12182,17 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>201</v>
+        <v>519</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>202</v>
+        <v>520</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12073,19 +12241,19 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>204</v>
+        <v>518</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>81</v>
@@ -12094,7 +12262,7 @@
         <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>205</v>
+        <v>523</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
@@ -12105,21 +12273,21 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>555</v>
+        <v>524</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>555</v>
+        <v>524</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
@@ -12131,16 +12299,16 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>135</v>
+        <v>295</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>208</v>
+        <v>525</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>209</v>
+        <v>526</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>183</v>
+        <v>527</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12190,19 +12358,19 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>211</v>
+        <v>524</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>81</v>
@@ -12211,7 +12379,7 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>205</v>
+        <v>528</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -12222,46 +12390,42 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>556</v>
+        <v>529</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>556</v>
+        <v>529</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>290</v>
+        <v>202</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
       </c>
@@ -12309,19 +12473,19 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>292</v>
+        <v>204</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>81</v>
@@ -12330,7 +12494,7 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -12341,10 +12505,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12352,10 +12516,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
@@ -12367,13 +12531,13 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>558</v>
+        <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>559</v>
+        <v>136</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>560</v>
+        <v>137</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12412,56 +12576,56 @@
         <v>81</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC88" s="2"/>
       <c r="AD88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>557</v>
+        <v>211</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>561</v>
+        <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>562</v>
+        <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>531</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="D89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12482,17 +12646,15 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>110</v>
+        <v>533</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>534</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12517,13 +12679,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -12541,28 +12703,28 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>564</v>
+        <v>211</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>81</v>
+        <v>536</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -12573,44 +12735,46 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>571</v>
+        <v>537</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>571</v>
+        <v>537</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>572</v>
+        <v>303</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>573</v>
+        <v>304</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
       </c>
@@ -12634,13 +12798,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>576</v>
+        <v>81</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12658,19 +12822,19 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>571</v>
+        <v>305</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>81</v>
@@ -12679,7 +12843,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -12690,10 +12854,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12716,13 +12880,13 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>578</v>
+        <v>539</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>579</v>
+        <v>540</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12773,7 +12937,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12788,27 +12952,27 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>81</v>
+        <v>541</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>387</v>
+        <v>192</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>81</v>
+        <v>542</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>580</v>
+        <v>543</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>580</v>
+        <v>543</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12816,7 +12980,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>90</v>
@@ -12831,13 +12995,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>581</v>
+        <v>544</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>582</v>
+        <v>545</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>583</v>
+        <v>546</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12888,7 +13052,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>580</v>
+        <v>543</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12903,27 +13067,27 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>584</v>
+        <v>547</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>585</v>
+        <v>548</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>586</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>587</v>
+        <v>549</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>587</v>
+        <v>549</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12946,17 +13110,15 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>588</v>
+        <v>225</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -12981,13 +13143,13 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>81</v>
+        <v>552</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>81</v>
+        <v>553</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
@@ -13005,7 +13167,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>587</v>
+        <v>549</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13023,15 +13185,1873 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AN93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO93" t="s" s="2">
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO109" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/441-rc---tdduipatient-birthdate/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/441-rc---tdduipatient-birthdate/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:28:52+00:00</t>
+    <t>2026-02-26T17:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
